--- a/astro-site/public/dl/kit-tareas-chocolateria/04-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/04-tareas-perfiles.xlsx
@@ -694,7 +694,7 @@
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+          <t>Versión 2.1 · octubre 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Verificar el etiquetado de cada referencia: precio, precio por kilo si se vende al peso, y los alérgenos declarados (leche, frutos secos, soja, gluten, huevo y sésamo) más las trazas</t>
+          <t>Verificar el etiquetado de cada referencia: precio, precio por kilo si se vende al peso, y los alérgenos declarados (leche, huevo, cereales con gluten, soja, cacahuetes, frutos de cáscara, sésamo y sulfitos) más las trazas</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">

--- a/astro-site/public/dl/kit-tareas-chocolateria/04-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/04-tareas-perfiles.xlsx
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Retirar productos de vitrina para conservación</t>
+          <t>Retirar productos de vitrina para conservación (la ganache de nata fresca y las trufas de nata, a la cámara de 0-4 °C)</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
